--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-14.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH114"/>
+  <dimension ref="A1:BH113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,170 +757,170 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.9</v>
+        <v>2.74</v>
       </c>
       <c r="G2" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="H2" t="n">
-        <v>2.48</v>
+        <v>2.58</v>
       </c>
       <c r="I2" t="n">
-        <v>2.72</v>
+        <v>2.86</v>
       </c>
       <c r="J2" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K2" t="n">
         <v>3.7</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="P2" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="G3" t="n">
         <v>3.3</v>
@@ -960,7 +960,7 @@
         <v>2.24</v>
       </c>
       <c r="I3" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="J3" t="n">
         <v>3.9</v>
@@ -969,10 +969,10 @@
         <v>4.3</v>
       </c>
       <c r="L3" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="M3" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N3" t="n">
         <v>5.5</v>
@@ -984,13 +984,13 @@
         <v>2.56</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="R3" t="n">
         <v>1.63</v>
       </c>
       <c r="S3" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="T3" t="n">
         <v>1.54</v>
@@ -999,13 +999,13 @@
         <v>2.6</v>
       </c>
       <c r="V3" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="W3" t="n">
         <v>1.44</v>
       </c>
       <c r="X3" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y3" t="n">
         <v>16</v>
@@ -1020,13 +1020,13 @@
         <v>22</v>
       </c>
       <c r="AC3" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD3" t="n">
         <v>12</v>
       </c>
       <c r="AE3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AF3" t="n">
         <v>30</v>
@@ -1035,7 +1035,7 @@
         <v>14.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI3" t="n">
         <v>32</v>
@@ -1059,7 +1059,7 @@
         <v>11.5</v>
       </c>
       <c r="AP3" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AQ3" t="n">
         <v>13</v>
@@ -1086,7 +1086,7 @@
         <v>21</v>
       </c>
       <c r="AY3" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AZ3" t="n">
         <v>13</v>
@@ -1095,16 +1095,16 @@
         <v>20</v>
       </c>
       <c r="BB3" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BC3" t="n">
         <v>24</v>
       </c>
       <c r="BD3" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BE3" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BF3" t="n">
         <v>16</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -1145,13 +1145,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="G4" t="n">
         <v>2.8</v>
       </c>
       <c r="H4" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="I4" t="n">
         <v>2.64</v>
@@ -1166,7 +1166,7 @@
         <v>1.2</v>
       </c>
       <c r="M4" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N4" t="n">
         <v>6.6</v>
@@ -1178,13 +1178,13 @@
         <v>2.92</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="R4" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="S4" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="T4" t="n">
         <v>1.45</v>
@@ -1202,10 +1202,10 @@
         <v>40</v>
       </c>
       <c r="Y4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Z4" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AA4" t="n">
         <v>44</v>
@@ -1214,7 +1214,7 @@
         <v>22</v>
       </c>
       <c r="AC4" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD4" t="n">
         <v>13.5</v>
@@ -1223,7 +1223,7 @@
         <v>28</v>
       </c>
       <c r="AF4" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AG4" t="n">
         <v>14</v>
@@ -1253,16 +1253,16 @@
         <v>11.5</v>
       </c>
       <c r="AP4" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="AQ4" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AR4" t="n">
         <v>19</v>
       </c>
       <c r="AS4" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="AT4" t="n">
         <v>17</v>
@@ -1289,7 +1289,7 @@
         <v>19.5</v>
       </c>
       <c r="BB4" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BC4" t="n">
         <v>20</v>
@@ -1298,7 +1298,7 @@
         <v>20</v>
       </c>
       <c r="BE4" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BF4" t="n">
         <v>10.5</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -1342,10 +1342,10 @@
         <v>2.16</v>
       </c>
       <c r="G5" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="H5" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="I5" t="n">
         <v>3.45</v>
@@ -1369,10 +1369,10 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -2124,7 +2124,7 @@
         <v>3.6</v>
       </c>
       <c r="I9" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="J9" t="n">
         <v>3.05</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -2318,7 +2318,7 @@
         <v>1.54</v>
       </c>
       <c r="I10" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="J10" t="n">
         <v>3.9</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -2503,7 +2503,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.2</v>
+        <v>1.04</v>
       </c>
       <c r="G11" t="n">
         <v>1.91</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -3285,7 +3285,7 @@
         <v>2.58</v>
       </c>
       <c r="H15" t="n">
-        <v>3.2</v>
+        <v>1.74</v>
       </c>
       <c r="I15" t="n">
         <v>4.4</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -3473,19 +3473,19 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="G16" t="n">
         <v>3.05</v>
       </c>
       <c r="H16" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="I16" t="n">
         <v>2.94</v>
       </c>
       <c r="J16" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K16" t="n">
         <v>3.8</v>
@@ -3503,10 +3503,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -3667,28 +3667,28 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.88</v>
+        <v>2.98</v>
       </c>
       <c r="G17" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="H17" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="I17" t="n">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
       <c r="J17" t="n">
         <v>3.45</v>
       </c>
       <c r="K17" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -3700,7 +3700,7 @@
         <v>1.24</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -3724,13 +3724,13 @@
         <v>21</v>
       </c>
       <c r="Y17" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Z17" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AB17" t="n">
         <v>16.5</v>
@@ -3739,7 +3739,7 @@
         <v>10.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE17" t="n">
         <v>30</v>
@@ -3751,64 +3751,64 @@
         <v>16.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI17" t="n">
         <v>44</v>
       </c>
       <c r="AJ17" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AK17" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AL17" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AM17" t="n">
         <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AO17" t="n">
         <v>21</v>
       </c>
       <c r="AP17" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AQ17" t="n">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="AR17" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AS17" t="n">
-        <v>3.8</v>
+        <v>22</v>
       </c>
       <c r="AT17" t="n">
         <v>10</v>
       </c>
       <c r="AU17" t="n">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="AV17" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AY17" t="n">
         <v>10</v>
       </c>
-      <c r="AW17" t="n">
-        <v>20</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>19</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>11</v>
-      </c>
       <c r="AZ17" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BA17" t="n">
-        <v>3.85</v>
+        <v>25</v>
       </c>
       <c r="BB17" t="n">
         <v>3.95</v>
@@ -3823,14 +3823,14 @@
         <v>4</v>
       </c>
       <c r="BF17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BG17" t="n">
         <v>12.5</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -4058,7 +4058,7 @@
         <v>2.76</v>
       </c>
       <c r="G19" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="H19" t="n">
         <v>2.58</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -4252,7 +4252,7 @@
         <v>3.3</v>
       </c>
       <c r="G20" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="H20" t="n">
         <v>2.26</v>
@@ -4261,7 +4261,7 @@
         <v>2.34</v>
       </c>
       <c r="J20" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K20" t="n">
         <v>3.75</v>
@@ -4279,7 +4279,7 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2.02</v>
+        <v>1.25</v>
       </c>
       <c r="Q20" t="n">
         <v>1.01</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -4861,10 +4861,10 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -5058,7 +5058,7 @@
         <v>1.53</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.34</v>
+        <v>2.52</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -5091,7 +5091,7 @@
         <v>1000</v>
       </c>
       <c r="AB24" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AC24" t="n">
         <v>8.4</v>
@@ -5136,22 +5136,22 @@
         <v>3.1</v>
       </c>
       <c r="AQ24" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="AR24" t="n">
         <v>16</v>
       </c>
       <c r="AS24" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AT24" t="n">
         <v>3</v>
       </c>
       <c r="AU24" t="n">
-        <v>2.88</v>
+        <v>6.2</v>
       </c>
       <c r="AV24" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="AW24" t="n">
         <v>4.1</v>
@@ -5160,10 +5160,10 @@
         <v>11</v>
       </c>
       <c r="AY24" t="n">
-        <v>9.4</v>
+        <v>3.45</v>
       </c>
       <c r="AZ24" t="n">
-        <v>16.5</v>
+        <v>3.8</v>
       </c>
       <c r="BA24" t="n">
         <v>4.2</v>
@@ -5175,20 +5175,20 @@
         <v>4</v>
       </c>
       <c r="BD24" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BE24" t="n">
         <v>4.3</v>
       </c>
       <c r="BF24" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BG24" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -5222,10 +5222,10 @@
         <v>2.02</v>
       </c>
       <c r="G25" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="H25" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="I25" t="n">
         <v>4.5</v>
@@ -5234,7 +5234,7 @@
         <v>3.55</v>
       </c>
       <c r="K25" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -5249,10 +5249,10 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.78</v>
+        <v>1.84</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="G26" t="n">
         <v>2.24</v>
@@ -5428,7 +5428,7 @@
         <v>3.45</v>
       </c>
       <c r="K26" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -5610,13 +5610,13 @@
         <v>2.8</v>
       </c>
       <c r="G27" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="H27" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="I27" t="n">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="J27" t="n">
         <v>3.4</v>
@@ -5649,7 +5649,7 @@
         <v>3.9</v>
       </c>
       <c r="T27" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="U27" t="n">
         <v>2.1</v>
@@ -5667,7 +5667,7 @@
         <v>10.5</v>
       </c>
       <c r="Z27" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AA27" t="n">
         <v>44</v>
@@ -5691,7 +5691,7 @@
         <v>13</v>
       </c>
       <c r="AH27" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI27" t="n">
         <v>60</v>
@@ -5715,7 +5715,7 @@
         <v>32</v>
       </c>
       <c r="AP27" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AQ27" t="n">
         <v>9.6</v>
@@ -5727,16 +5727,16 @@
         <v>24</v>
       </c>
       <c r="AT27" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AU27" t="n">
         <v>6.8</v>
       </c>
       <c r="AV27" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AW27" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AX27" t="n">
         <v>16</v>
@@ -5766,11 +5766,11 @@
         <v>20</v>
       </c>
       <c r="BG27" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -5995,19 +5995,19 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="G29" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="H29" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="I29" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="J29" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K29" t="n">
         <v>4.8</v>
@@ -6025,7 +6025,7 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q29" t="n">
         <v>1.78</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -6219,10 +6219,10 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -6580,19 +6580,19 @@
         <v>1.72</v>
       </c>
       <c r="G32" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="H32" t="n">
         <v>4</v>
       </c>
       <c r="I32" t="n">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="J32" t="n">
         <v>3.4</v>
       </c>
       <c r="K32" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -6965,19 +6965,19 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="G34" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="H34" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="I34" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="J34" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="K34" t="n">
         <v>4.2</v>
@@ -6995,7 +6995,7 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="Q34" t="n">
         <v>1.89</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -7165,7 +7165,7 @@
         <v>1.59</v>
       </c>
       <c r="H35" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="I35" t="n">
         <v>6.6</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -7750,7 +7750,7 @@
         <v>3.55</v>
       </c>
       <c r="I38" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="J38" t="n">
         <v>3.05</v>
@@ -7771,10 +7771,10 @@
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -7938,13 +7938,13 @@
         <v>2.62</v>
       </c>
       <c r="G39" t="n">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="H39" t="n">
-        <v>1.25</v>
+        <v>2.26</v>
       </c>
       <c r="I39" t="n">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="J39" t="n">
         <v>3.5</v>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -8526,7 +8526,7 @@
         <v>5.9</v>
       </c>
       <c r="I42" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="J42" t="n">
         <v>4.6</v>
@@ -8541,7 +8541,7 @@
         <v>1.04</v>
       </c>
       <c r="N42" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="O42" t="n">
         <v>1.2</v>
@@ -8550,19 +8550,19 @@
         <v>2.52</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="R42" t="n">
         <v>1.61</v>
       </c>
       <c r="S42" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="T42" t="n">
         <v>1.73</v>
       </c>
       <c r="U42" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
@@ -8622,7 +8622,7 @@
         <v>6.4</v>
       </c>
       <c r="AO42" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AP42" t="n">
         <v>21</v>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="G43" t="n">
         <v>5.7</v>
@@ -8831,7 +8831,7 @@
         <v>16.5</v>
       </c>
       <c r="AT43" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="AU43" t="n">
         <v>11</v>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -8929,13 +8929,13 @@
         <v>1.03</v>
       </c>
       <c r="N44" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="O44" t="n">
         <v>1.19</v>
       </c>
       <c r="P44" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="Q44" t="n">
         <v>1.57</v>
@@ -8983,7 +8983,7 @@
         <v>1000</v>
       </c>
       <c r="AF44" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AG44" t="n">
         <v>10.5</v>
@@ -9004,7 +9004,7 @@
         <v>30</v>
       </c>
       <c r="AM44" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AN44" t="n">
         <v>5.3</v>
@@ -9068,7 +9068,7 @@
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -9293,7 +9293,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="G46" t="n">
         <v>3.4</v>
@@ -9302,7 +9302,7 @@
         <v>2.4</v>
       </c>
       <c r="I46" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="J46" t="n">
         <v>3.15</v>
@@ -9456,7 +9456,7 @@
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -9490,16 +9490,16 @@
         <v>2.84</v>
       </c>
       <c r="G47" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="H47" t="n">
         <v>2.56</v>
       </c>
       <c r="I47" t="n">
-        <v>2.84</v>
+        <v>3.05</v>
       </c>
       <c r="J47" t="n">
-        <v>2.98</v>
+        <v>2.92</v>
       </c>
       <c r="K47" t="n">
         <v>3.6</v>
@@ -9520,7 +9520,7 @@
         <v>1.66</v>
       </c>
       <c r="Q47" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="R47" t="n">
         <v>0</v>
@@ -9650,7 +9650,7 @@
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -9681,13 +9681,13 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="G48" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="H48" t="n">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="I48" t="n">
         <v>8.6</v>
@@ -9696,7 +9696,7 @@
         <v>4.2</v>
       </c>
       <c r="K48" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="Q48" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="R48" t="n">
         <v>0</v>
@@ -9844,7 +9844,7 @@
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -9881,10 +9881,10 @@
         <v>2.86</v>
       </c>
       <c r="H49" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="I49" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="J49" t="n">
         <v>3</v>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -10232,7 +10232,7 @@
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -10293,7 +10293,7 @@
         <v>1.52</v>
       </c>
       <c r="P51" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="Q51" t="n">
         <v>2.48</v>
@@ -10329,7 +10329,7 @@
         <v>1000</v>
       </c>
       <c r="AB51" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="AC51" t="n">
         <v>9</v>
@@ -10377,7 +10377,7 @@
         <v>17</v>
       </c>
       <c r="AR51" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AS51" t="n">
         <v>110</v>
@@ -10404,7 +10404,7 @@
         <v>27</v>
       </c>
       <c r="BA51" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BB51" t="n">
         <v>13.5</v>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -10466,7 +10466,7 @@
         <v>2.28</v>
       </c>
       <c r="I52" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="J52" t="n">
         <v>3.55</v>
@@ -10620,7 +10620,7 @@
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -10845,13 +10845,13 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="G54" t="n">
         <v>2.5</v>
       </c>
       <c r="H54" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="I54" t="n">
         <v>3.15</v>
@@ -10875,7 +10875,7 @@
         <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="Q54" t="n">
         <v>1.63</v>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -11202,7 +11202,7 @@
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -11236,7 +11236,7 @@
         <v>1.88</v>
       </c>
       <c r="G56" t="n">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="H56" t="n">
         <v>3.45</v>
@@ -11248,7 +11248,7 @@
         <v>3.35</v>
       </c>
       <c r="K56" t="n">
-        <v>950</v>
+        <v>4.1</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
@@ -11396,7 +11396,7 @@
       </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -11433,16 +11433,16 @@
         <v>2.24</v>
       </c>
       <c r="H57" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="I57" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="J57" t="n">
         <v>3.35</v>
       </c>
       <c r="K57" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
@@ -11460,7 +11460,7 @@
         <v>2.1</v>
       </c>
       <c r="Q57" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="R57" t="n">
         <v>0</v>
@@ -11590,7 +11590,7 @@
       </c>
       <c r="BH57" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -11627,7 +11627,7 @@
         <v>4.7</v>
       </c>
       <c r="H58" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="I58" t="n">
         <v>1.96</v>
@@ -11784,7 +11784,7 @@
       </c>
       <c r="BH58" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -11806,31 +11806,31 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>SV Ried</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>WSG Wattens</t>
+          <t>RZ Pellets WAC</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>2</v>
+        <v>2.72</v>
       </c>
       <c r="G59" t="n">
-        <v>2.16</v>
+        <v>3.1</v>
       </c>
       <c r="H59" t="n">
-        <v>4.1</v>
+        <v>2.72</v>
       </c>
       <c r="I59" t="n">
-        <v>5</v>
+        <v>3.05</v>
       </c>
       <c r="J59" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="K59" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
@@ -11845,10 +11845,10 @@
         <v>0</v>
       </c>
       <c r="P59" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="Q59" t="n">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="R59" t="n">
         <v>0</v>
@@ -11978,7 +11978,7 @@
       </c>
       <c r="BH59" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -12000,31 +12000,31 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>SV Ried</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RZ Pellets WAC</t>
+          <t>WSG Wattens</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>2.72</v>
+        <v>2</v>
       </c>
       <c r="G60" t="n">
-        <v>3.1</v>
+        <v>2.16</v>
       </c>
       <c r="H60" t="n">
-        <v>2.72</v>
+        <v>4.1</v>
       </c>
       <c r="I60" t="n">
-        <v>3.05</v>
+        <v>5</v>
       </c>
       <c r="J60" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="K60" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
@@ -12039,10 +12039,10 @@
         <v>0</v>
       </c>
       <c r="P60" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="Q60" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="R60" t="n">
         <v>0</v>
@@ -12172,7 +12172,7 @@
       </c>
       <c r="BH60" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -12206,10 +12206,10 @@
         <v>2.18</v>
       </c>
       <c r="G61" t="n">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="H61" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="I61" t="n">
         <v>4.1</v>
@@ -12218,7 +12218,7 @@
         <v>3.05</v>
       </c>
       <c r="K61" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
@@ -12366,7 +12366,7 @@
       </c>
       <c r="BH61" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -12397,22 +12397,22 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="G62" t="n">
-        <v>2.56</v>
+        <v>2.38</v>
       </c>
       <c r="H62" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="I62" t="n">
-        <v>4.9</v>
+        <v>3.85</v>
       </c>
       <c r="J62" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="K62" t="n">
-        <v>4.4</v>
+        <v>3.75</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
@@ -12430,7 +12430,7 @@
         <v>1.71</v>
       </c>
       <c r="Q62" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="R62" t="n">
         <v>0</v>
@@ -12560,7 +12560,7 @@
       </c>
       <c r="BH62" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -12597,7 +12597,7 @@
         <v>2.02</v>
       </c>
       <c r="H63" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="I63" t="n">
         <v>8.199999999999999</v>
@@ -12606,7 +12606,7 @@
         <v>3.05</v>
       </c>
       <c r="K63" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="L63" t="n">
         <v>1.01</v>
@@ -12754,7 +12754,7 @@
       </c>
       <c r="BH63" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -12788,7 +12788,7 @@
         <v>2.54</v>
       </c>
       <c r="G64" t="n">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="H64" t="n">
         <v>2.6</v>
@@ -12948,14 +12948,14 @@
       </c>
       <c r="BH64" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Turkish Super League</t>
+          <t>Italian Serie A</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -12970,61 +12970,61 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>1.79</v>
+        <v>1.37</v>
       </c>
       <c r="G65" t="n">
-        <v>1.87</v>
+        <v>1.39</v>
       </c>
       <c r="H65" t="n">
-        <v>4.5</v>
+        <v>11.5</v>
       </c>
       <c r="I65" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="J65" t="n">
         <v>5.2</v>
       </c>
-      <c r="J65" t="n">
-        <v>3.9</v>
-      </c>
       <c r="K65" t="n">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O65" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="P65" t="n">
-        <v>2.44</v>
+        <v>1.76</v>
       </c>
       <c r="Q65" t="n">
-        <v>1.68</v>
+        <v>2.24</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S65" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="T65" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="U65" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="V65" t="n">
         <v>0</v>
@@ -13033,123 +13033,123 @@
         <v>0</v>
       </c>
       <c r="X65" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="Y65" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="Z65" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AA65" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB65" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AC65" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AD65" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AE65" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF65" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AG65" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AH65" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AI65" t="n">
-        <v>0</v>
+        <v>330</v>
       </c>
       <c r="AJ65" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AK65" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AL65" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AM65" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN65" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AO65" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP65" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AQ65" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AR65" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AS65" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AT65" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AU65" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AV65" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AW65" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AX65" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AY65" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AZ65" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BA65" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="BB65" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="BC65" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BD65" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="BE65" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="BF65" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BG65" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="BH65" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Italian Serie A</t>
+          <t>Swiss Challenge League</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -13164,28 +13164,28 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>1.37</v>
+        <v>1.54</v>
       </c>
       <c r="G66" t="n">
-        <v>1.39</v>
+        <v>1.66</v>
       </c>
       <c r="H66" t="n">
-        <v>11.5</v>
+        <v>5.6</v>
       </c>
       <c r="I66" t="n">
-        <v>12.5</v>
+        <v>7.6</v>
       </c>
       <c r="J66" t="n">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="K66" t="n">
         <v>5.3</v>
@@ -13194,31 +13194,31 @@
         <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="P66" t="n">
-        <v>1.76</v>
+        <v>2.62</v>
       </c>
       <c r="Q66" t="n">
-        <v>2.24</v>
+        <v>1.51</v>
       </c>
       <c r="R66" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S66" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="T66" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="U66" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="V66" t="n">
         <v>0</v>
@@ -13227,123 +13227,123 @@
         <v>0</v>
       </c>
       <c r="X66" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="Z66" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB66" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AC66" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AD66" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AE66" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF66" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="AG66" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AH66" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="AI66" t="n">
-        <v>330</v>
+        <v>0</v>
       </c>
       <c r="AJ66" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AK66" t="n">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="AL66" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="AM66" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN66" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="AO66" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP66" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AQ66" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AR66" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="AS66" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AT66" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AU66" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AV66" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="AW66" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="AX66" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="AY66" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AZ66" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="BA66" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="BB66" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="BC66" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="BD66" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="BE66" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="BF66" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="BG66" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="BH66" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Swiss Challenge League</t>
+          <t>Turkish 1 Lig</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -13358,31 +13358,31 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Istanbulspor</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>1.56</v>
+        <v>1.71</v>
       </c>
       <c r="G67" t="n">
-        <v>1.69</v>
+        <v>2.18</v>
       </c>
       <c r="H67" t="n">
-        <v>5.3</v>
+        <v>3.6</v>
       </c>
       <c r="I67" t="n">
-        <v>7.2</v>
+        <v>5.7</v>
       </c>
       <c r="J67" t="n">
-        <v>4.6</v>
+        <v>3.45</v>
       </c>
       <c r="K67" t="n">
-        <v>5.3</v>
+        <v>7.4</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
@@ -13397,10 +13397,10 @@
         <v>0</v>
       </c>
       <c r="P67" t="n">
-        <v>2.66</v>
+        <v>1.98</v>
       </c>
       <c r="Q67" t="n">
-        <v>1.51</v>
+        <v>1.58</v>
       </c>
       <c r="R67" t="n">
         <v>0</v>
@@ -13530,14 +13530,14 @@
       </c>
       <c r="BH67" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Turkish 1 Lig</t>
+          <t>Turkish Super League</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -13552,31 +13552,31 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Istanbulspor</t>
+          <t>Basaksehir</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="G68" t="n">
-        <v>2.18</v>
+        <v>1.77</v>
       </c>
       <c r="H68" t="n">
-        <v>3.6</v>
+        <v>4.7</v>
       </c>
       <c r="I68" t="n">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="J68" t="n">
-        <v>3.45</v>
+        <v>4.3</v>
       </c>
       <c r="K68" t="n">
-        <v>7.4</v>
+        <v>4.8</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
@@ -13591,10 +13591,10 @@
         <v>0</v>
       </c>
       <c r="P68" t="n">
-        <v>1.98</v>
+        <v>2.5</v>
       </c>
       <c r="Q68" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="R68" t="n">
         <v>0</v>
@@ -13724,7 +13724,7 @@
       </c>
       <c r="BH68" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -13746,31 +13746,31 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Goztepe</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Basaksehir</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>1.68</v>
+        <v>2.2</v>
       </c>
       <c r="G69" t="n">
-        <v>1.77</v>
+        <v>2.34</v>
       </c>
       <c r="H69" t="n">
-        <v>4.7</v>
+        <v>3.7</v>
       </c>
       <c r="I69" t="n">
-        <v>5.2</v>
+        <v>4</v>
       </c>
       <c r="J69" t="n">
-        <v>4.3</v>
+        <v>3.15</v>
       </c>
       <c r="K69" t="n">
-        <v>4.8</v>
+        <v>3.5</v>
       </c>
       <c r="L69" t="n">
         <v>0</v>
@@ -13785,10 +13785,10 @@
         <v>0</v>
       </c>
       <c r="P69" t="n">
-        <v>2.5</v>
+        <v>1.64</v>
       </c>
       <c r="Q69" t="n">
-        <v>1.55</v>
+        <v>2.26</v>
       </c>
       <c r="R69" t="n">
         <v>0</v>
@@ -13918,7 +13918,7 @@
       </c>
       <c r="BH69" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -13940,31 +13940,31 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Goztepe</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>2.2</v>
+        <v>1.79</v>
       </c>
       <c r="G70" t="n">
-        <v>2.34</v>
+        <v>1.86</v>
       </c>
       <c r="H70" t="n">
-        <v>3.7</v>
+        <v>4.6</v>
       </c>
       <c r="I70" t="n">
-        <v>4</v>
+        <v>5.2</v>
       </c>
       <c r="J70" t="n">
-        <v>3.15</v>
+        <v>3.9</v>
       </c>
       <c r="K70" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="L70" t="n">
         <v>0</v>
@@ -13979,10 +13979,10 @@
         <v>0</v>
       </c>
       <c r="P70" t="n">
-        <v>1.65</v>
+        <v>2.44</v>
       </c>
       <c r="Q70" t="n">
-        <v>2.26</v>
+        <v>1.68</v>
       </c>
       <c r="R70" t="n">
         <v>0</v>
@@ -14112,7 +14112,7 @@
       </c>
       <c r="BH70" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -14149,7 +14149,7 @@
         <v>2.16</v>
       </c>
       <c r="H71" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I71" t="n">
         <v>4.8</v>
@@ -14306,7 +14306,7 @@
       </c>
       <c r="BH71" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -14349,7 +14349,7 @@
         <v>2.52</v>
       </c>
       <c r="J72" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K72" t="n">
         <v>3.8</v>
@@ -14500,7 +14500,7 @@
       </c>
       <c r="BH72" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -14570,7 +14570,7 @@
         <v>1.44</v>
       </c>
       <c r="S73" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="T73" t="n">
         <v>1.71</v>
@@ -14636,7 +14636,7 @@
         <v>15</v>
       </c>
       <c r="AO73" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AP73" t="n">
         <v>15</v>
@@ -14694,7 +14694,7 @@
       </c>
       <c r="BH73" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -14725,7 +14725,7 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="G74" t="n">
         <v>3.1</v>
@@ -14734,10 +14734,10 @@
         <v>2.72</v>
       </c>
       <c r="I74" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="J74" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K74" t="n">
         <v>3.3</v>
@@ -14788,7 +14788,7 @@
         <v>16.5</v>
       </c>
       <c r="AA74" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AB74" t="n">
         <v>9.4</v>
@@ -14833,7 +14833,7 @@
         <v>42</v>
       </c>
       <c r="AP74" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ74" t="n">
         <v>8.199999999999999</v>
@@ -14888,7 +14888,7 @@
       </c>
       <c r="BH74" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -14922,19 +14922,19 @@
         <v>1.48</v>
       </c>
       <c r="G75" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="H75" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="I75" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="J75" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="K75" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="L75" t="n">
         <v>0</v>
@@ -14949,7 +14949,7 @@
         <v>0</v>
       </c>
       <c r="P75" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="Q75" t="n">
         <v>1.31</v>
@@ -15082,7 +15082,7 @@
       </c>
       <c r="BH75" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -15134,10 +15134,10 @@
         <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N76" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="O76" t="n">
         <v>1.38</v>
@@ -15155,7 +15155,7 @@
         <v>3.9</v>
       </c>
       <c r="T76" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="U76" t="n">
         <v>2.1</v>
@@ -15188,7 +15188,7 @@
         <v>12</v>
       </c>
       <c r="AE76" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AF76" t="n">
         <v>23</v>
@@ -15197,10 +15197,10 @@
         <v>14.5</v>
       </c>
       <c r="AH76" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AI76" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ76" t="n">
         <v>60</v>
@@ -15212,13 +15212,13 @@
         <v>55</v>
       </c>
       <c r="AM76" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AN76" t="n">
         <v>42</v>
       </c>
       <c r="AO76" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AP76" t="n">
         <v>11</v>
@@ -15230,7 +15230,7 @@
         <v>14</v>
       </c>
       <c r="AS76" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AT76" t="n">
         <v>10.5</v>
@@ -15254,36 +15254,36 @@
         <v>16</v>
       </c>
       <c r="BA76" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BB76" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BC76" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="BD76" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BE76" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BF76" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="BG76" t="n">
         <v>21</v>
       </c>
       <c r="BH76" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Polish I Liga</t>
+          <t>Hungarian NB I</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -15298,31 +15298,31 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Ruch Chorzow</t>
+          <t>Debreceni VSC</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Nyiregyhaza</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>1.77</v>
+        <v>1.91</v>
       </c>
       <c r="G77" t="n">
-        <v>2.28</v>
+        <v>2.46</v>
       </c>
       <c r="H77" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="I77" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="J77" t="n">
-        <v>2.78</v>
+        <v>3.2</v>
       </c>
       <c r="K77" t="n">
-        <v>8</v>
+        <v>5.7</v>
       </c>
       <c r="L77" t="n">
         <v>0</v>
@@ -15337,10 +15337,10 @@
         <v>0</v>
       </c>
       <c r="P77" t="n">
-        <v>1.92</v>
+        <v>1.67</v>
       </c>
       <c r="Q77" t="n">
-        <v>1.63</v>
+        <v>1.87</v>
       </c>
       <c r="R77" t="n">
         <v>0</v>
@@ -15470,14 +15470,14 @@
       </c>
       <c r="BH77" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Hungarian NB I</t>
+          <t>Italian Serie B</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -15492,31 +15492,31 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Debreceni VSC</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Nyiregyhaza</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>1.91</v>
+        <v>4.5</v>
       </c>
       <c r="G78" t="n">
-        <v>2.46</v>
+        <v>5.7</v>
       </c>
       <c r="H78" t="n">
-        <v>3.35</v>
+        <v>1.86</v>
       </c>
       <c r="I78" t="n">
-        <v>5.2</v>
+        <v>2.28</v>
       </c>
       <c r="J78" t="n">
-        <v>3.2</v>
+        <v>2.94</v>
       </c>
       <c r="K78" t="n">
-        <v>5.7</v>
+        <v>4</v>
       </c>
       <c r="L78" t="n">
         <v>0</v>
@@ -15531,10 +15531,10 @@
         <v>0</v>
       </c>
       <c r="P78" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="Q78" t="n">
-        <v>1.87</v>
+        <v>1.98</v>
       </c>
       <c r="R78" t="n">
         <v>0</v>
@@ -15664,14 +15664,14 @@
       </c>
       <c r="BH78" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Italian Serie B</t>
+          <t>Polish I Liga</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -15686,31 +15686,31 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Ruch Chorzow</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>4.3</v>
+        <v>1.77</v>
       </c>
       <c r="G79" t="n">
-        <v>5.9</v>
+        <v>2.28</v>
       </c>
       <c r="H79" t="n">
-        <v>1.86</v>
+        <v>3.25</v>
       </c>
       <c r="I79" t="n">
-        <v>2.28</v>
+        <v>4.9</v>
       </c>
       <c r="J79" t="n">
-        <v>2.94</v>
+        <v>2.78</v>
       </c>
       <c r="K79" t="n">
-        <v>4.4</v>
+        <v>8</v>
       </c>
       <c r="L79" t="n">
         <v>0</v>
@@ -15725,10 +15725,10 @@
         <v>0</v>
       </c>
       <c r="P79" t="n">
-        <v>1.71</v>
+        <v>1.92</v>
       </c>
       <c r="Q79" t="n">
-        <v>1.98</v>
+        <v>1.63</v>
       </c>
       <c r="R79" t="n">
         <v>0</v>
@@ -15858,7 +15858,7 @@
       </c>
       <c r="BH79" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -16052,7 +16052,7 @@
       </c>
       <c r="BH80" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -16074,31 +16074,31 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Al-Khaleej Saihat</t>
+          <t>Al-Shabab (KSA)</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al-Akhdoud</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>8.199999999999999</v>
+        <v>1.33</v>
       </c>
       <c r="G81" t="n">
-        <v>11.5</v>
+        <v>1.5</v>
       </c>
       <c r="H81" t="n">
-        <v>1.35</v>
+        <v>3</v>
       </c>
       <c r="I81" t="n">
-        <v>1.42</v>
+        <v>29</v>
       </c>
       <c r="J81" t="n">
-        <v>5.7</v>
+        <v>4.7</v>
       </c>
       <c r="K81" t="n">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="L81" t="n">
         <v>0</v>
@@ -16113,7 +16113,7 @@
         <v>0</v>
       </c>
       <c r="P81" t="n">
-        <v>2.88</v>
+        <v>2.24</v>
       </c>
       <c r="Q81" t="n">
         <v>1.46</v>
@@ -16246,7 +16246,7 @@
       </c>
       <c r="BH81" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -16268,31 +16268,31 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Al-Fateh (KSA)</t>
+          <t>Al-Khaleej Saihat</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Al-Hilal</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>2.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G82" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="H82" t="n">
-        <v>1.09</v>
+        <v>1.35</v>
       </c>
       <c r="I82" t="n">
-        <v>1.91</v>
+        <v>1.42</v>
       </c>
       <c r="J82" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="K82" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="L82" t="n">
         <v>0</v>
@@ -16307,10 +16307,10 @@
         <v>0</v>
       </c>
       <c r="P82" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="Q82" t="n">
-        <v>1.25</v>
+        <v>1.46</v>
       </c>
       <c r="R82" t="n">
         <v>0</v>
@@ -16440,7 +16440,7 @@
       </c>
       <c r="BH82" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -16471,16 +16471,16 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="G83" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="H83" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="I83" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="J83" t="n">
         <v>2.84</v>
@@ -16634,7 +16634,7 @@
       </c>
       <c r="BH83" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -16656,28 +16656,28 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Al-Shabab (KSA)</t>
+          <t>Al-Fateh (KSA)</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Al-Akhdoud</t>
+          <t>Al-Hilal</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>1.33</v>
+        <v>2.1</v>
       </c>
       <c r="G84" t="n">
-        <v>1.5</v>
+        <v>1000</v>
       </c>
       <c r="H84" t="n">
-        <v>3</v>
+        <v>1.04</v>
       </c>
       <c r="I84" t="n">
-        <v>29</v>
+        <v>1.91</v>
       </c>
       <c r="J84" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="K84" t="n">
         <v>1000</v>
@@ -16695,10 +16695,10 @@
         <v>0</v>
       </c>
       <c r="P84" t="n">
-        <v>2.24</v>
+        <v>2.92</v>
       </c>
       <c r="Q84" t="n">
-        <v>1.46</v>
+        <v>1.25</v>
       </c>
       <c r="R84" t="n">
         <v>0</v>
@@ -16828,7 +16828,7 @@
       </c>
       <c r="BH84" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -16859,13 +16859,13 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="G85" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="H85" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I85" t="n">
         <v>4.9</v>
@@ -16889,7 +16889,7 @@
         <v>0</v>
       </c>
       <c r="P85" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="Q85" t="n">
         <v>1.52</v>
@@ -17022,7 +17022,7 @@
       </c>
       <c r="BH85" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -17053,41 +17053,41 @@
         </is>
       </c>
       <c r="F86" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="G86" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H86" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="I86" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="J86" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="K86" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="L86" t="n">
+        <v>0</v>
+      </c>
+      <c r="M86" t="n">
+        <v>0</v>
+      </c>
+      <c r="N86" t="n">
+        <v>0</v>
+      </c>
+      <c r="O86" t="n">
+        <v>0</v>
+      </c>
+      <c r="P86" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Q86" t="n">
         <v>2.78</v>
       </c>
-      <c r="G86" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="H86" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="I86" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="J86" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="K86" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="L86" t="n">
-        <v>0</v>
-      </c>
-      <c r="M86" t="n">
-        <v>0</v>
-      </c>
-      <c r="N86" t="n">
-        <v>0</v>
-      </c>
-      <c r="O86" t="n">
-        <v>0</v>
-      </c>
-      <c r="P86" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="Q86" t="n">
-        <v>2.56</v>
-      </c>
       <c r="R86" t="n">
         <v>0</v>
       </c>
@@ -17216,7 +17216,7 @@
       </c>
       <c r="BH86" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -17247,22 +17247,22 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="G87" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="H87" t="n">
         <v>1.72</v>
       </c>
       <c r="I87" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="J87" t="n">
         <v>3.75</v>
       </c>
       <c r="K87" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L87" t="n">
         <v>0</v>
@@ -17410,7 +17410,7 @@
       </c>
       <c r="BH87" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -17441,22 +17441,22 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="G88" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="H88" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="I88" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="J88" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K88" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L88" t="n">
         <v>0</v>
@@ -17604,7 +17604,7 @@
       </c>
       <c r="BH88" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -17641,7 +17641,7 @@
         <v>2.2</v>
       </c>
       <c r="H89" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="I89" t="n">
         <v>3.6</v>
@@ -17798,7 +17798,7 @@
       </c>
       <c r="BH89" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -17832,10 +17832,10 @@
         <v>6.8</v>
       </c>
       <c r="G90" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="H90" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="I90" t="n">
         <v>1.61</v>
@@ -17967,7 +17967,7 @@
         <v>20</v>
       </c>
       <c r="AZ90" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BA90" t="n">
         <v>36</v>
@@ -17992,7 +17992,7 @@
       </c>
       <c r="BH90" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -18026,7 +18026,7 @@
         <v>2.86</v>
       </c>
       <c r="G91" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="H91" t="n">
         <v>3.15</v>
@@ -18186,7 +18186,7 @@
       </c>
       <c r="BH91" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -18217,22 +18217,22 @@
         </is>
       </c>
       <c r="F92" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="G92" t="n">
         <v>1.73</v>
       </c>
       <c r="H92" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="I92" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="J92" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K92" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="L92" t="n">
         <v>0</v>
@@ -18247,10 +18247,10 @@
         <v>0</v>
       </c>
       <c r="P92" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="Q92" t="n">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="R92" t="n">
         <v>0</v>
@@ -18380,7 +18380,7 @@
       </c>
       <c r="BH92" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -18417,16 +18417,16 @@
         <v>1.3</v>
       </c>
       <c r="H93" t="n">
+        <v>11</v>
+      </c>
+      <c r="I93" t="n">
         <v>12</v>
       </c>
-      <c r="I93" t="n">
-        <v>12.5</v>
-      </c>
       <c r="J93" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="K93" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="L93" t="n">
         <v>0</v>
@@ -18447,7 +18447,7 @@
         <v>1.45</v>
       </c>
       <c r="R93" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="S93" t="n">
         <v>2.16</v>
@@ -18465,10 +18465,10 @@
         <v>0</v>
       </c>
       <c r="X93" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Y93" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="Z93" t="n">
         <v>1000</v>
@@ -18486,7 +18486,7 @@
         <v>50</v>
       </c>
       <c r="AE93" t="n">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="AF93" t="n">
         <v>9.800000000000001</v>
@@ -18510,16 +18510,16 @@
         <v>30</v>
       </c>
       <c r="AM93" t="n">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="AN93" t="n">
         <v>3.8</v>
       </c>
       <c r="AO93" t="n">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="AP93" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ93" t="n">
         <v>25</v>
@@ -18543,7 +18543,7 @@
         <v>44</v>
       </c>
       <c r="AX93" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AY93" t="n">
         <v>9.6</v>
@@ -18574,7 +18574,7 @@
       </c>
       <c r="BH93" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -18605,19 +18605,19 @@
         </is>
       </c>
       <c r="F94" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="G94" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="H94" t="n">
         <v>2.48</v>
       </c>
       <c r="I94" t="n">
-        <v>3.1</v>
+        <v>2.78</v>
       </c>
       <c r="J94" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K94" t="n">
         <v>3.65</v>
@@ -18635,10 +18635,10 @@
         <v>0</v>
       </c>
       <c r="P94" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="Q94" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="R94" t="n">
         <v>0</v>
@@ -18734,7 +18734,7 @@
         <v>10</v>
       </c>
       <c r="AW94" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AX94" t="n">
         <v>17.5</v>
@@ -18768,7 +18768,7 @@
       </c>
       <c r="BH94" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -18799,7 +18799,7 @@
         </is>
       </c>
       <c r="F95" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="G95" t="n">
         <v>3.15</v>
@@ -18962,7 +18962,7 @@
       </c>
       <c r="BH95" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -19017,7 +19017,7 @@
         <v>1.05</v>
       </c>
       <c r="N96" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="O96" t="n">
         <v>1.21</v>
@@ -19026,7 +19026,7 @@
         <v>2.34</v>
       </c>
       <c r="Q96" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="R96" t="n">
         <v>1.5</v>
@@ -19035,7 +19035,7 @@
         <v>2.6</v>
       </c>
       <c r="T96" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="U96" t="n">
         <v>2.28</v>
@@ -19056,7 +19056,7 @@
         <v>46</v>
       </c>
       <c r="AA96" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AB96" t="n">
         <v>11</v>
@@ -19071,7 +19071,7 @@
         <v>65</v>
       </c>
       <c r="AF96" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AG96" t="n">
         <v>10.5</v>
@@ -19080,13 +19080,13 @@
         <v>19</v>
       </c>
       <c r="AI96" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ96" t="n">
         <v>17.5</v>
       </c>
       <c r="AK96" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AL96" t="n">
         <v>32</v>
@@ -19110,10 +19110,10 @@
         <v>36</v>
       </c>
       <c r="AS96" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AT96" t="n">
         <v>10</v>
-      </c>
-      <c r="AT96" t="n">
-        <v>9.6</v>
       </c>
       <c r="AU96" t="n">
         <v>9</v>
@@ -19122,7 +19122,7 @@
         <v>17</v>
       </c>
       <c r="AW96" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AX96" t="n">
         <v>10</v>
@@ -19152,11 +19152,11 @@
         <v>7.4</v>
       </c>
       <c r="BG96" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BH96" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -19350,14 +19350,14 @@
       </c>
       <c r="BH97" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Chilean Primera B</t>
+          <t>Chilean Primera Division</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -19372,31 +19372,31 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Universidad de Chile</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>1.04</v>
+        <v>2.68</v>
       </c>
       <c r="G98" t="n">
-        <v>1000</v>
+        <v>3.1</v>
       </c>
       <c r="H98" t="n">
-        <v>1.04</v>
+        <v>2.82</v>
       </c>
       <c r="I98" t="n">
-        <v>1000</v>
+        <v>3.3</v>
       </c>
       <c r="J98" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="K98" t="n">
-        <v>950</v>
+        <v>3.7</v>
       </c>
       <c r="L98" t="n">
         <v>0</v>
@@ -19411,10 +19411,10 @@
         <v>0</v>
       </c>
       <c r="P98" t="n">
-        <v>1.24</v>
+        <v>1.68</v>
       </c>
       <c r="Q98" t="n">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="R98" t="n">
         <v>0</v>
@@ -19544,14 +19544,14 @@
       </c>
       <c r="BH98" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Chilean Primera Division</t>
+          <t>Chilean Primera B</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -19566,31 +19566,31 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Universidad de Chile</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F99" t="n">
-        <v>2.62</v>
+        <v>1.04</v>
       </c>
       <c r="G99" t="n">
-        <v>3.15</v>
+        <v>1000</v>
       </c>
       <c r="H99" t="n">
-        <v>2.84</v>
+        <v>1.04</v>
       </c>
       <c r="I99" t="n">
-        <v>3.5</v>
+        <v>1000</v>
       </c>
       <c r="J99" t="n">
-        <v>2.92</v>
+        <v>1.01</v>
       </c>
       <c r="K99" t="n">
-        <v>3.8</v>
+        <v>950</v>
       </c>
       <c r="L99" t="n">
         <v>0</v>
@@ -19605,10 +19605,10 @@
         <v>0</v>
       </c>
       <c r="P99" t="n">
-        <v>1.64</v>
+        <v>1.24</v>
       </c>
       <c r="Q99" t="n">
-        <v>2.18</v>
+        <v>1.01</v>
       </c>
       <c r="R99" t="n">
         <v>0</v>
@@ -19738,7 +19738,7 @@
       </c>
       <c r="BH99" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -19772,19 +19772,19 @@
         <v>3.15</v>
       </c>
       <c r="G100" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="H100" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="I100" t="n">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="J100" t="n">
-        <v>2.86</v>
+        <v>3.1</v>
       </c>
       <c r="K100" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L100" t="n">
         <v>0</v>
@@ -19932,7 +19932,7 @@
       </c>
       <c r="BH100" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -19963,10 +19963,10 @@
         </is>
       </c>
       <c r="F101" t="n">
-        <v>2.62</v>
+        <v>2.4</v>
       </c>
       <c r="G101" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="H101" t="n">
         <v>2.84</v>
@@ -19975,10 +19975,10 @@
         <v>3.55</v>
       </c>
       <c r="J101" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="K101" t="n">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="L101" t="n">
         <v>0</v>
@@ -20126,7 +20126,7 @@
       </c>
       <c r="BH101" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -20320,7 +20320,7 @@
       </c>
       <c r="BH102" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -20514,7 +20514,7 @@
       </c>
       <c r="BH103" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -20708,7 +20708,7 @@
       </c>
       <c r="BH104" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -20742,7 +20742,7 @@
         <v>1.65</v>
       </c>
       <c r="G105" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="H105" t="n">
         <v>2.28</v>
@@ -20902,7 +20902,7 @@
       </c>
       <c r="BH105" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -20936,19 +20936,19 @@
         <v>2.72</v>
       </c>
       <c r="G106" t="n">
-        <v>3.15</v>
+        <v>2.96</v>
       </c>
       <c r="H106" t="n">
         <v>2.6</v>
       </c>
       <c r="I106" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="J106" t="n">
         <v>3.4</v>
       </c>
       <c r="K106" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L106" t="n">
         <v>0</v>
@@ -20966,7 +20966,7 @@
         <v>1.97</v>
       </c>
       <c r="Q106" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="R106" t="n">
         <v>0</v>
@@ -21096,7 +21096,7 @@
       </c>
       <c r="BH106" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -21130,7 +21130,7 @@
         <v>1.25</v>
       </c>
       <c r="G107" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="H107" t="n">
         <v>12</v>
@@ -21290,14 +21290,14 @@
       </c>
       <c r="BH107" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Honduras Liga Nacional</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -21307,36 +21307,36 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>20:15:00</t>
+          <t>20:20:00</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Olancho</t>
+          <t>Boyaca Chico</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Real Espana</t>
+          <t>Millonarios</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="G108" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="H108" t="n">
-        <v>1.04</v>
+        <v>1.79</v>
       </c>
       <c r="I108" t="n">
-        <v>1000</v>
+        <v>1.99</v>
       </c>
       <c r="J108" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="K108" t="n">
-        <v>950</v>
+        <v>3.75</v>
       </c>
       <c r="L108" t="n">
         <v>0</v>
@@ -21351,10 +21351,10 @@
         <v>0</v>
       </c>
       <c r="P108" t="n">
-        <v>1.24</v>
+        <v>1.46</v>
       </c>
       <c r="Q108" t="n">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="R108" t="n">
         <v>0</v>
@@ -21484,14 +21484,14 @@
       </c>
       <c r="BH108" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -21501,36 +21501,36 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>20:20:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Boyaca Chico</t>
+          <t>Albion FC</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Millonarios</t>
+          <t>Penarol</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>5.3</v>
+        <v>4.7</v>
       </c>
       <c r="G109" t="n">
-        <v>7.4</v>
+        <v>6.2</v>
       </c>
       <c r="H109" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="I109" t="n">
-        <v>1.99</v>
+        <v>1.88</v>
       </c>
       <c r="J109" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="K109" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="L109" t="n">
         <v>0</v>
@@ -21545,10 +21545,10 @@
         <v>0</v>
       </c>
       <c r="P109" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="Q109" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="R109" t="n">
         <v>0</v>
@@ -21678,14 +21678,14 @@
       </c>
       <c r="BH109" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Chilean Primera Division</t>
+          <t>Brazilian Serie A</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -21700,31 +21700,31 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Univ Catolica (Chile)</t>
+          <t>Botafogo FR</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Everton De Vina</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>1.6</v>
+        <v>3.65</v>
       </c>
       <c r="G110" t="n">
-        <v>1.72</v>
+        <v>5</v>
       </c>
       <c r="H110" t="n">
-        <v>5.3</v>
+        <v>1.81</v>
       </c>
       <c r="I110" t="n">
-        <v>7</v>
+        <v>2.36</v>
       </c>
       <c r="J110" t="n">
-        <v>3.75</v>
+        <v>2.64</v>
       </c>
       <c r="K110" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="L110" t="n">
         <v>0</v>
@@ -21739,10 +21739,10 @@
         <v>0</v>
       </c>
       <c r="P110" t="n">
-        <v>1.74</v>
+        <v>1.25</v>
       </c>
       <c r="Q110" t="n">
-        <v>1.84</v>
+        <v>2.04</v>
       </c>
       <c r="R110" t="n">
         <v>0</v>
@@ -21872,14 +21872,14 @@
       </c>
       <c r="BH110" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Chilean Primera B</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -21894,31 +21894,31 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Albion FC</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Penarol</t>
+          <t>Deportes Copiapo</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>4.6</v>
+        <v>1.04</v>
       </c>
       <c r="G111" t="n">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="H111" t="n">
-        <v>1.76</v>
+        <v>1.04</v>
       </c>
       <c r="I111" t="n">
-        <v>1.89</v>
+        <v>1000</v>
       </c>
       <c r="J111" t="n">
-        <v>3.45</v>
+        <v>1.01</v>
       </c>
       <c r="K111" t="n">
-        <v>4.2</v>
+        <v>950</v>
       </c>
       <c r="L111" t="n">
         <v>0</v>
@@ -21933,10 +21933,10 @@
         <v>0</v>
       </c>
       <c r="P111" t="n">
-        <v>1.44</v>
+        <v>1.24</v>
       </c>
       <c r="Q111" t="n">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="R111" t="n">
         <v>0</v>
@@ -22066,14 +22066,14 @@
       </c>
       <c r="BH111" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Chilean Primera Division</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -22088,31 +22088,31 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Botafogo FR</t>
+          <t>Univ Catolica (Chile)</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Everton De Vina</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>3.65</v>
+        <v>1.6</v>
       </c>
       <c r="G112" t="n">
-        <v>5.3</v>
+        <v>1.7</v>
       </c>
       <c r="H112" t="n">
-        <v>1.23</v>
+        <v>5.4</v>
       </c>
       <c r="I112" t="n">
-        <v>2.36</v>
+        <v>7</v>
       </c>
       <c r="J112" t="n">
-        <v>2.58</v>
+        <v>3.75</v>
       </c>
       <c r="K112" t="n">
-        <v>950</v>
+        <v>4.5</v>
       </c>
       <c r="L112" t="n">
         <v>0</v>
@@ -22127,10 +22127,10 @@
         <v>0</v>
       </c>
       <c r="P112" t="n">
-        <v>1.25</v>
+        <v>1.74</v>
       </c>
       <c r="Q112" t="n">
-        <v>2.04</v>
+        <v>1.84</v>
       </c>
       <c r="R112" t="n">
         <v>0</v>
@@ -22260,14 +22260,14 @@
       </c>
       <c r="BH112" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Chilean Primera B</t>
+          <t>Venezuelan Primera Division</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -22282,12 +22282,12 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Monagas</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Deportes Copiapo</t>
+          <t>Academia Anzoategui FC</t>
         </is>
       </c>
       <c r="F113" t="n">
@@ -22454,201 +22454,7 @@
       </c>
       <c r="BH113" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>Venezuelan Primera Division</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>20:30:00</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>Monagas</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>Academia Anzoategui FC</t>
-        </is>
-      </c>
-      <c r="F114" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="G114" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H114" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="I114" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J114" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="K114" t="n">
-        <v>950</v>
-      </c>
-      <c r="L114" t="n">
-        <v>0</v>
-      </c>
-      <c r="M114" t="n">
-        <v>0</v>
-      </c>
-      <c r="N114" t="n">
-        <v>0</v>
-      </c>
-      <c r="O114" t="n">
-        <v>0</v>
-      </c>
-      <c r="P114" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q114" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R114" t="n">
-        <v>0</v>
-      </c>
-      <c r="S114" t="n">
-        <v>0</v>
-      </c>
-      <c r="T114" t="n">
-        <v>0</v>
-      </c>
-      <c r="U114" t="n">
-        <v>0</v>
-      </c>
-      <c r="V114" t="n">
-        <v>0</v>
-      </c>
-      <c r="W114" t="n">
-        <v>0</v>
-      </c>
-      <c r="X114" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y114" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z114" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA114" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB114" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC114" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD114" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE114" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF114" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG114" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH114" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI114" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ114" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK114" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL114" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM114" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN114" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO114" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP114" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ114" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR114" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS114" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT114" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU114" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV114" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW114" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX114" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY114" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ114" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA114" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB114" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC114" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD114" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE114" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF114" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG114" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH114" t="inlineStr">
-        <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
